--- a/CLIENT/DATExx-Whiddon/Roles.xlsx
+++ b/CLIENT/DATExx-Whiddon/Roles.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alex\CentriNOTSYNC\ResidentialCare\CLIENT\DATExx-Whiddon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51B3DDD2-21BC-4102-9BE8-73B0B3B77B22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23D53E16-6E07-4388-93ED-1F97E222AC3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="19440" windowHeight="21120" xr2:uid="{ED27A41B-61EF-4CBA-8C9E-3A94836D14E9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{ED27A41B-61EF-4CBA-8C9E-3A94836D14E9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -305,15 +305,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -360,31 +360,6 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="7"/>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -428,13 +403,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color theme="7" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <right style="thin">
           <color theme="7" tint="0.39997558519241921"/>
         </right>
@@ -445,6 +413,38 @@
           <color theme="7" tint="0.39997558519241921"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="7" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="7"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -539,11 +539,11 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{50A60422-E134-475E-84F1-53061D689559}" name="RoleAnalysis" displayName="RoleAnalysis" ref="A28:C43" totalsRowShown="0" headerRowDxfId="1" headerRowBorderDxfId="4" tableBorderDxfId="5" totalsRowBorderDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{50A60422-E134-475E-84F1-53061D689559}" name="RoleAnalysis" displayName="RoleAnalysis" ref="A28:C43" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4" tableBorderDxfId="3" totalsRowBorderDxfId="2">
   <autoFilter ref="A28:C43" xr:uid="{50A60422-E134-475E-84F1-53061D689559}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{7E8D0824-8226-4D37-9D8A-5734FD7722C0}" name="Roles"/>
-    <tableColumn id="3" xr3:uid="{E302BC0E-3DEE-4C9D-A698-D2F3F77F8B8D}" name="Leave Balance Analysis" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{E302BC0E-3DEE-4C9D-A698-D2F3F77F8B8D}" name="Leave Balance Analysis" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{1D75BF6C-CDF4-460D-AD50-25866C5F45C7}" name="Effort Management Analysis" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
